--- a/panchang-data/Bangalore2026.xlsx
+++ b/panchang-data/Bangalore2026.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5377">
   <si>
     <t>दिनाङ्क</t>
   </si>
@@ -16156,6 +16156,9 @@
   </si>
   <si>
     <t>121°05'07.47</t>
+  </si>
+  <si>
+    <t>ज्येष्ठ अधिक</t>
   </si>
 </sst>
 </file>
@@ -16645,7 +16648,7 @@
         <v>46023</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>29</v>
@@ -16731,7 +16734,7 @@
         <v>46024</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>50</v>
@@ -16817,7 +16820,7 @@
         <v>46025</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>70</v>
@@ -16903,7 +16906,7 @@
         <v>46026</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>89</v>
@@ -16989,7 +16992,7 @@
         <v>46027</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>108</v>
@@ -17075,7 +17078,7 @@
         <v>46028</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>125</v>
@@ -17161,7 +17164,7 @@
         <v>46029</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>143</v>
@@ -17247,7 +17250,7 @@
         <v>46030</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>29</v>
@@ -17333,7 +17336,7 @@
         <v>46031</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>50</v>
@@ -17419,7 +17422,7 @@
         <v>46032</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>70</v>
@@ -17505,7 +17508,7 @@
         <v>46033</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>89</v>
@@ -17591,7 +17594,7 @@
         <v>46034</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>108</v>
@@ -17677,7 +17680,7 @@
         <v>46035</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>125</v>
@@ -17763,7 +17766,7 @@
         <v>46036</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>143</v>
@@ -17849,7 +17852,7 @@
         <v>46037</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>29</v>
@@ -17935,7 +17938,7 @@
         <v>46038</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>50</v>
@@ -18021,7 +18024,7 @@
         <v>46039</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>70</v>
@@ -18107,7 +18110,7 @@
         <v>46040</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>89</v>
@@ -18193,7 +18196,7 @@
         <v>46041</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>108</v>
@@ -18279,7 +18282,7 @@
         <v>46042</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>125</v>
@@ -18365,7 +18368,7 @@
         <v>46043</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>143</v>
@@ -18451,7 +18454,7 @@
         <v>46044</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>29</v>
@@ -18537,7 +18540,7 @@
         <v>46045</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>50</v>
@@ -18623,7 +18626,7 @@
         <v>46046</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>70</v>
@@ -18709,7 +18712,7 @@
         <v>46047</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>89</v>
@@ -18795,7 +18798,7 @@
         <v>46048</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>108</v>
@@ -18881,7 +18884,7 @@
         <v>46049</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>125</v>
@@ -18967,7 +18970,7 @@
         <v>46050</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>143</v>
@@ -19053,7 +19056,7 @@
         <v>46051</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>29</v>
@@ -19139,7 +19142,7 @@
         <v>46052</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>50</v>
@@ -19225,7 +19228,7 @@
         <v>46053</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>70</v>
@@ -19311,7 +19314,7 @@
         <v>46054</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>88</v>
+        <v>563</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>89</v>
@@ -19397,7 +19400,7 @@
         <v>46055</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>563</v>
+        <v>1005</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>108</v>
@@ -19483,7 +19486,7 @@
         <v>46056</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>563</v>
+        <v>1005</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>125</v>
@@ -19569,7 +19572,7 @@
         <v>46057</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>563</v>
+        <v>1005</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>143</v>
@@ -19655,7 +19658,7 @@
         <v>46058</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>563</v>
+        <v>1005</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>29</v>
@@ -19741,7 +19744,7 @@
         <v>46059</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>563</v>
+        <v>1005</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>50</v>
@@ -19827,7 +19830,7 @@
         <v>46060</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>563</v>
+        <v>1005</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>70</v>
@@ -19913,7 +19916,7 @@
         <v>46061</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>563</v>
+        <v>1005</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>89</v>
@@ -19999,7 +20002,7 @@
         <v>46062</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>563</v>
+        <v>1005</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>108</v>
@@ -20085,7 +20088,7 @@
         <v>46063</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>563</v>
+        <v>1005</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>125</v>
@@ -20171,7 +20174,7 @@
         <v>46064</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>563</v>
+        <v>1005</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>143</v>
@@ -20257,7 +20260,7 @@
         <v>46065</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>563</v>
+        <v>1005</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>29</v>
@@ -20343,7 +20346,7 @@
         <v>46066</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>563</v>
+        <v>1005</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>50</v>
@@ -20429,7 +20432,7 @@
         <v>46067</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>563</v>
+        <v>1005</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>70</v>
@@ -20515,7 +20518,7 @@
         <v>46068</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>563</v>
+        <v>1005</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>89</v>
@@ -20601,7 +20604,7 @@
         <v>46069</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>563</v>
+        <v>1005</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>108</v>
@@ -20687,7 +20690,7 @@
         <v>46070</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>563</v>
+        <v>1005</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>125</v>
@@ -20773,7 +20776,7 @@
         <v>46071</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>563</v>
+        <v>1005</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>143</v>
@@ -20859,7 +20862,7 @@
         <v>46072</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>563</v>
+        <v>1005</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>29</v>
@@ -20945,7 +20948,7 @@
         <v>46073</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>563</v>
+        <v>1005</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>50</v>
@@ -21031,7 +21034,7 @@
         <v>46074</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>563</v>
+        <v>1005</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>70</v>
@@ -21117,7 +21120,7 @@
         <v>46075</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>563</v>
+        <v>1005</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>89</v>
@@ -21203,7 +21206,7 @@
         <v>46076</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>563</v>
+        <v>1005</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>108</v>
@@ -21289,7 +21292,7 @@
         <v>46077</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>563</v>
+        <v>1005</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>125</v>
@@ -21375,7 +21378,7 @@
         <v>46078</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>563</v>
+        <v>1005</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>143</v>
@@ -21461,7 +21464,7 @@
         <v>46079</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>563</v>
+        <v>1005</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>29</v>
@@ -21547,7 +21550,7 @@
         <v>46080</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>563</v>
+        <v>1005</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>50</v>
@@ -21633,7 +21636,7 @@
         <v>46081</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>563</v>
+        <v>1005</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>70</v>
@@ -21719,7 +21722,7 @@
         <v>46082</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>563</v>
+        <v>1005</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>89</v>
@@ -21805,7 +21808,7 @@
         <v>46083</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>563</v>
+        <v>1005</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>108</v>
@@ -21891,7 +21894,7 @@
         <v>46084</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>563</v>
+        <v>1005</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>125</v>
@@ -21977,7 +21980,7 @@
         <v>46085</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>1005</v>
+        <v>1445</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>143</v>
@@ -22063,7 +22066,7 @@
         <v>46086</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>1005</v>
+        <v>1445</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>29</v>
@@ -22149,7 +22152,7 @@
         <v>46087</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>1005</v>
+        <v>1445</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>50</v>
@@ -22235,7 +22238,7 @@
         <v>46088</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>1005</v>
+        <v>1445</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>70</v>
@@ -22321,7 +22324,7 @@
         <v>46089</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>1005</v>
+        <v>1445</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>89</v>
@@ -22407,7 +22410,7 @@
         <v>46090</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>1005</v>
+        <v>1445</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>108</v>
@@ -22493,7 +22496,7 @@
         <v>46091</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>1005</v>
+        <v>1445</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>125</v>
@@ -22579,7 +22582,7 @@
         <v>46092</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>1005</v>
+        <v>1445</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>143</v>
@@ -22665,7 +22668,7 @@
         <v>46093</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>1005</v>
+        <v>1445</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>29</v>
@@ -22751,7 +22754,7 @@
         <v>46094</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>1005</v>
+        <v>1445</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>50</v>
@@ -22837,7 +22840,7 @@
         <v>46095</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>1005</v>
+        <v>1445</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>70</v>
@@ -22923,7 +22926,7 @@
         <v>46096</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>1005</v>
+        <v>1445</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>89</v>
@@ -23009,7 +23012,7 @@
         <v>46097</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>1005</v>
+        <v>1445</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>108</v>
@@ -23095,7 +23098,7 @@
         <v>46098</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>1005</v>
+        <v>1445</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>125</v>
@@ -23181,7 +23184,7 @@
         <v>46099</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>1005</v>
+        <v>1445</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>143</v>
@@ -23267,7 +23270,7 @@
         <v>46100</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>1005</v>
+        <v>1445</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>29</v>
@@ -23353,7 +23356,7 @@
         <v>46101</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>1005</v>
+        <v>1445</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>50</v>
@@ -23439,7 +23442,7 @@
         <v>46102</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>1005</v>
+        <v>1445</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>70</v>
@@ -23525,7 +23528,7 @@
         <v>46103</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>1005</v>
+        <v>1445</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>89</v>
@@ -23611,7 +23614,7 @@
         <v>46104</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>1005</v>
+        <v>1445</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>108</v>
@@ -23697,7 +23700,7 @@
         <v>46105</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>1005</v>
+        <v>1445</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>125</v>
@@ -23783,7 +23786,7 @@
         <v>46106</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>1005</v>
+        <v>1445</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>143</v>
@@ -23869,7 +23872,7 @@
         <v>46107</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>1005</v>
+        <v>1445</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>29</v>
@@ -23955,7 +23958,7 @@
         <v>46108</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>1005</v>
+        <v>1445</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>50</v>
@@ -24041,7 +24044,7 @@
         <v>46109</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>1005</v>
+        <v>1445</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>70</v>
@@ -24127,7 +24130,7 @@
         <v>46110</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>1005</v>
+        <v>1445</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>89</v>
@@ -24213,7 +24216,7 @@
         <v>46111</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>1005</v>
+        <v>1445</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>108</v>
@@ -24299,7 +24302,7 @@
         <v>46112</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>1005</v>
+        <v>1445</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>125</v>
@@ -24385,7 +24388,7 @@
         <v>46113</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>1005</v>
+        <v>1445</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>143</v>
@@ -24471,7 +24474,7 @@
         <v>46114</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>1005</v>
+        <v>1445</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>29</v>
@@ -24557,7 +24560,7 @@
         <v>46115</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>1445</v>
+        <v>1869</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>50</v>
@@ -24643,7 +24646,7 @@
         <v>46116</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>1445</v>
+        <v>1869</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>70</v>
@@ -24729,7 +24732,7 @@
         <v>46117</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>1445</v>
+        <v>1869</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>89</v>
@@ -24815,7 +24818,7 @@
         <v>46118</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>1445</v>
+        <v>1869</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>108</v>
@@ -24901,7 +24904,7 @@
         <v>46119</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>1445</v>
+        <v>1869</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>125</v>
@@ -24987,7 +24990,7 @@
         <v>46120</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>1445</v>
+        <v>1869</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>143</v>
@@ -25073,7 +25076,7 @@
         <v>46121</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>1445</v>
+        <v>1869</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>29</v>
@@ -25159,7 +25162,7 @@
         <v>46122</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1445</v>
+        <v>1869</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>50</v>
@@ -25245,7 +25248,7 @@
         <v>46123</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>1445</v>
+        <v>1869</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>70</v>
@@ -25331,7 +25334,7 @@
         <v>46124</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>1445</v>
+        <v>1869</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>89</v>
@@ -25417,7 +25420,7 @@
         <v>46125</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>1445</v>
+        <v>1869</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>108</v>
@@ -25503,7 +25506,7 @@
         <v>46126</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>1445</v>
+        <v>1869</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>125</v>
@@ -25589,7 +25592,7 @@
         <v>46127</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>1445</v>
+        <v>1869</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>143</v>
@@ -25675,7 +25678,7 @@
         <v>46128</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>1445</v>
+        <v>1869</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>29</v>
@@ -25761,7 +25764,7 @@
         <v>46129</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>1445</v>
+        <v>1869</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>50</v>
@@ -25847,7 +25850,7 @@
         <v>46130</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>1445</v>
+        <v>1869</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>70</v>
@@ -25933,7 +25936,7 @@
         <v>46131</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>1445</v>
+        <v>1869</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>89</v>
@@ -26019,7 +26022,7 @@
         <v>46132</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>1445</v>
+        <v>1869</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>108</v>
@@ -26105,7 +26108,7 @@
         <v>46133</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>1445</v>
+        <v>1869</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>125</v>
@@ -26191,7 +26194,7 @@
         <v>46134</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>1445</v>
+        <v>1869</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>143</v>
@@ -26277,7 +26280,7 @@
         <v>46135</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>1445</v>
+        <v>1869</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>29</v>
@@ -26363,7 +26366,7 @@
         <v>46136</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>1445</v>
+        <v>1869</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>50</v>
@@ -26449,7 +26452,7 @@
         <v>46137</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>1445</v>
+        <v>1869</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>70</v>
@@ -26535,7 +26538,7 @@
         <v>46138</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>1445</v>
+        <v>1869</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>89</v>
@@ -26621,7 +26624,7 @@
         <v>46139</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>1445</v>
+        <v>1869</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>108</v>
@@ -26707,7 +26710,7 @@
         <v>46140</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>1445</v>
+        <v>1869</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>125</v>
@@ -26793,7 +26796,7 @@
         <v>46141</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>1445</v>
+        <v>1869</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>143</v>
@@ -26879,7 +26882,7 @@
         <v>46142</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>1445</v>
+        <v>1869</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>29</v>
@@ -26965,7 +26968,7 @@
         <v>46143</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>1445</v>
+        <v>1869</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>50</v>
@@ -27051,7 +27054,7 @@
         <v>46144</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>1869</v>
+        <v>2306</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>70</v>
@@ -27137,7 +27140,7 @@
         <v>46145</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>1869</v>
+        <v>2306</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>89</v>
@@ -27223,7 +27226,7 @@
         <v>46146</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>1869</v>
+        <v>2306</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>108</v>
@@ -27309,7 +27312,7 @@
         <v>46147</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>1869</v>
+        <v>2306</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>125</v>
@@ -27395,7 +27398,7 @@
         <v>46148</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>1869</v>
+        <v>2306</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>143</v>
@@ -27481,7 +27484,7 @@
         <v>46149</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>1869</v>
+        <v>2306</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>29</v>
@@ -27567,7 +27570,7 @@
         <v>46150</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>1869</v>
+        <v>2306</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>50</v>
@@ -27653,7 +27656,7 @@
         <v>46151</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>1869</v>
+        <v>2306</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>70</v>
@@ -27739,7 +27742,7 @@
         <v>46152</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>1869</v>
+        <v>2306</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>89</v>
@@ -27825,7 +27828,7 @@
         <v>46153</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>1869</v>
+        <v>2306</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>108</v>
@@ -27911,7 +27914,7 @@
         <v>46154</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>1869</v>
+        <v>2306</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>125</v>
@@ -27997,7 +28000,7 @@
         <v>46155</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>1869</v>
+        <v>2306</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>143</v>
@@ -28083,7 +28086,7 @@
         <v>46156</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>1869</v>
+        <v>2306</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>29</v>
@@ -28169,7 +28172,7 @@
         <v>46157</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>1869</v>
+        <v>2306</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>50</v>
@@ -28255,7 +28258,7 @@
         <v>46158</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>1869</v>
+        <v>2306</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>70</v>
@@ -28341,7 +28344,7 @@
         <v>46159</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>1869</v>
+        <v>5376</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>89</v>
@@ -28427,7 +28430,7 @@
         <v>46160</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>1869</v>
+        <v>5376</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>108</v>
@@ -28513,7 +28516,7 @@
         <v>46161</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>1869</v>
+        <v>5376</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>125</v>
@@ -28599,7 +28602,7 @@
         <v>46162</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>1869</v>
+        <v>5376</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>143</v>
@@ -28685,7 +28688,7 @@
         <v>46163</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>1869</v>
+        <v>5376</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>29</v>
@@ -28771,7 +28774,7 @@
         <v>46164</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>1869</v>
+        <v>5376</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>50</v>
@@ -28857,7 +28860,7 @@
         <v>46165</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>1869</v>
+        <v>5376</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>70</v>
@@ -28943,7 +28946,7 @@
         <v>46166</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>1869</v>
+        <v>5376</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>89</v>
@@ -29029,7 +29032,7 @@
         <v>46167</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>1869</v>
+        <v>5376</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>108</v>
@@ -29115,7 +29118,7 @@
         <v>46168</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>1869</v>
+        <v>5376</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>125</v>
@@ -29201,7 +29204,7 @@
         <v>46169</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>1869</v>
+        <v>5376</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>143</v>
@@ -29287,7 +29290,7 @@
         <v>46170</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>1869</v>
+        <v>5376</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>29</v>
@@ -29373,7 +29376,7 @@
         <v>46171</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>1869</v>
+        <v>5376</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>50</v>
@@ -29459,7 +29462,7 @@
         <v>46172</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>1869</v>
+        <v>5376</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>70</v>
@@ -29545,7 +29548,7 @@
         <v>46173</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>1869</v>
+        <v>5376</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>89</v>
@@ -29631,7 +29634,7 @@
         <v>46174</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>2306</v>
+        <v>5376</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>108</v>
@@ -29717,7 +29720,7 @@
         <v>46175</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>2306</v>
+        <v>5376</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>125</v>
@@ -29803,7 +29806,7 @@
         <v>46176</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>2306</v>
+        <v>5376</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>143</v>
@@ -29889,7 +29892,7 @@
         <v>46177</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>2306</v>
+        <v>5376</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>29</v>
@@ -29975,7 +29978,7 @@
         <v>46178</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>2306</v>
+        <v>5376</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>50</v>
@@ -30061,7 +30064,7 @@
         <v>46179</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>2306</v>
+        <v>5376</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>70</v>
@@ -30147,7 +30150,7 @@
         <v>46180</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>2306</v>
+        <v>5376</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>89</v>
@@ -30233,7 +30236,7 @@
         <v>46181</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>2306</v>
+        <v>5376</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>108</v>
@@ -30319,7 +30322,7 @@
         <v>46182</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>2306</v>
+        <v>5376</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>125</v>
@@ -30405,7 +30408,7 @@
         <v>46183</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>2306</v>
+        <v>5376</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>143</v>
@@ -30491,7 +30494,7 @@
         <v>46184</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>2306</v>
+        <v>5376</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>29</v>
@@ -30577,7 +30580,7 @@
         <v>46185</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>2306</v>
+        <v>5376</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>50</v>
@@ -30663,7 +30666,7 @@
         <v>46186</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>2306</v>
+        <v>5376</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>70</v>
@@ -30749,7 +30752,7 @@
         <v>46187</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>2306</v>
+        <v>5376</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>89</v>
@@ -30835,7 +30838,7 @@
         <v>46188</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>2306</v>
+        <v>5376</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>108</v>
